--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2023_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2023_nuble.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:56</t>
+    <t xml:space="preserve">2026-09-24 01:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -892,13 +892,13 @@
         <v>21</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="17">
@@ -915,13 +915,13 @@
         <v>21</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.07</v>
+        <v>0.05</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="18">
@@ -938,13 +938,13 @@
         <v>21</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="19">
@@ -1001,19 +1001,19 @@
         <v>31</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>21</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.19</v>
+        <v>0.06</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="22">
@@ -1024,19 +1024,19 @@
         <v>31</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.12</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.11</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="23">
@@ -1053,13 +1053,13 @@
         <v>21</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="24">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2023_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2023_nuble.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:45</t>
+    <t xml:space="preserve">2026-10-01 23:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -524,7 +524,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="31.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="33.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="14.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2023_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2023_nuble.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:19</t>
+    <t xml:space="preserve">2026-10-05 20:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
